--- a/assets/speaker_list_template.xlsx
+++ b/assets/speaker_list_template.xlsx
@@ -19,8 +19,30 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Optional free text - e.g. 'Moderator', 'Chief Guest', 'Keynote Speaker', 'Event Inauguration by'. Leave blank for a regular Speaker/Panelist (no label will be shown above their photo on the slide).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -31,7 +53,7 @@
     <t xml:space="preserve">Company</t>
   </si>
   <si>
-    <t xml:space="preserve">Moderator (Y/N)</t>
+    <t xml:space="preserve">Role</t>
   </si>
   <si>
     <t xml:space="preserve">Dr. Pankaj Dikshit</t>
@@ -43,7 +65,7 @@
     <t xml:space="preserve">Government e-Marketplace (GeM)</t>
   </si>
   <si>
-    <t xml:space="preserve">Y</t>
+    <t xml:space="preserve">Moderator</t>
   </si>
   <si>
     <t xml:space="preserve">Ashwin Raguraman</t>
@@ -53,9 +75,6 @@
   </si>
   <si>
     <t xml:space="preserve">Bharat Innovation Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
   </si>
   <si>
     <t xml:space="preserve">Raghu Venkatesh</t>
@@ -74,7 +93,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,6 +129,11 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -430,7 +454,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -471,31 +495,21 @@
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="D4" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="false" error="Please enter Y or N" errorStyle="stop" errorTitle="Invalid entry" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D200" type="list">
-      <formula1>"Y,N"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -503,5 +517,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>